--- a/Data/OHC_diff_totals_output_tindopac.xlsx
+++ b/Data/OHC_diff_totals_output_tindopac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\01.HarryGrosvenor\02.Research\05.Local_Repos\202404_01.PlioMIP2_ThetaO\Data\01.thetao\01.OneTime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C857FC6E-D597-4FA1-A5F8-EF29A2D54512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD7FCE6-E0A1-43CD-8307-DEECFFEE18F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OHC diffs Globally" sheetId="1" r:id="rId1"/>
@@ -557,21 +557,21 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>4.5396836716803917E+17</v>
       </c>
       <c r="C5">
-        <v>4.3275538950699568E+24</v>
+        <v>5.1330531732089327E+24</v>
       </c>
       <c r="D5">
-        <v>9532721.2379713822</v>
+        <v>11307072.35226568</v>
       </c>
       <c r="E5">
         <v>4.5934791384602522E+17</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>4.3788356139378532E+24</v>
+        <v>5.1938800967193096E+24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -773,11 +773,11 @@
       </c>
       <c r="C15" s="3">
         <f t="shared" ref="C15:F15" si="1" xml:space="preserve"> AVERAGE(C2:C14)</f>
-        <v>2.6805646444266684E+24</v>
+        <v>2.742526127360436E+24</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="1"/>
-        <v>6577497.370459659</v>
+        <v>6713985.9177130666</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="1"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
-        <v>2.7335637406387803E+24</v>
+        <v>2.7962594700835077E+24</v>
       </c>
     </row>
   </sheetData>
@@ -897,17 +897,17 @@
         <v>2.3458832373743048E+16</v>
       </c>
       <c r="C5">
-        <v>2.3495124783135641E+23</v>
+        <v>2.5375555468402479E+23</v>
       </c>
       <c r="D5">
-        <v>10015470.68021732</v>
+        <v>10817058.182659069</v>
       </c>
       <c r="E5">
         <v>2.37046883580827E+16</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>2.3741361123406612E+23</v>
+        <v>2.5641499317118163E+23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,11 +1109,11 @@
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">AVERAGE(C2:C14)</f>
-        <v>1.7467350592401406E+23</v>
+        <v>1.76119991066527E+23</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="1"/>
-        <v>7563090.7835550895</v>
+        <v>7624751.3606659928</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="1"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>1.764515193517841E+23</v>
+        <v>1.779131641161776E+23</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F16" s="5">
         <f>_xlfn.STDEV.P(F2:F14)</f>
-        <v>6.7797464184773537E+22</v>
+        <v>6.9284506635649969E+22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F17" s="6">
         <f>F16/F15</f>
-        <v>0.38422714881592224</v>
+        <v>0.38942878105639822</v>
       </c>
     </row>
   </sheetData>
